--- a/tasks/medical_pathfinder_billing_and_coding_bbf1a560/environment/initial_workspace/PBC_Claim_Register.xlsx
+++ b/tasks/medical_pathfinder_billing_and_coding_bbf1a560/environment/initial_workspace/PBC_Claim_Register.xlsx
@@ -3,6 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
   <workbookPr defaultThemeVersion="202300"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15"/>
+  </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E6BF7A8-F509-1F4A-B7EE-7162041B5BA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="46560" yWindow="580" windowWidth="20560" windowHeight="19240" xr2:uid="{624733F6-B685-8541-AFD1-3C47D5EAEBFD}"/>
